--- a/docs/ValueSet-BREstadoSolicitacaoMedicamento-1.0.xlsx
+++ b/docs/ValueSet-BREstadoSolicitacaoMedicamento-1.0.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -99,43 +99,43 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>Ativo</t>
+    <t>Active</t>
   </si>
   <si>
     <t>completed</t>
   </si>
   <si>
-    <t>Completado</t>
+    <t>Completed</t>
   </si>
   <si>
     <t>entered-in-error</t>
   </si>
   <si>
-    <t>Entrada com erro</t>
+    <t>Entered in Error</t>
   </si>
   <si>
     <t>draft</t>
   </si>
   <si>
-    <t>Pretendido</t>
+    <t>Draft</t>
   </si>
   <si>
     <t>on-hold</t>
   </si>
   <si>
-    <t>Em pausa</t>
+    <t>On Hold</t>
   </si>
   <si>
     <t>unknown</t>
   </si>
   <si>
-    <t>Desconhecida</t>
+    <t>Unknown</t>
   </si>
   <si>
     <t>cancelled</t>
   </si>
   <si>
-    <t>Não realizado</t>
+    <t>Cancelled</t>
   </si>
   <si>
     <t/>
